--- a/data.xlsx
+++ b/data.xlsx
@@ -696,7 +696,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -715,13 +715,6 @@
       <sz val="8"/>
       <name val="Tahoma"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -1279,28 +1272,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1309,118 +1305,115 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1793,8 +1786,7 @@
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="2" width="13.5" customWidth="1"/>
     <col min="4" max="4" width="15.5" customWidth="1"/>
-    <col min="5" max="5" width="68.6666666666667" customWidth="1"/>
-    <col min="6" max="6" width="68.6666666666667" customWidth="1"/>
+    <col min="5" max="6" width="68.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
